--- a/grupos/5ARHM - Estadisticos 20231.xlsx
+++ b/grupos/5ARHM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -71,9 +71,6 @@
     <t>CERON COCOTLE LAURA EVELYN</t>
   </si>
   <si>
-    <t>CHAVEZ DE GANTE YARETZI VALERIA</t>
-  </si>
-  <si>
     <t>CHAVEZ SANCHEZ JESUS MANUEL</t>
   </si>
   <si>
@@ -110,9 +107,6 @@
     <t>MENDEZ MARTINEZ AMY</t>
   </si>
   <si>
-    <t>MONTERO LOPEZ MARIA DEL PILAR</t>
-  </si>
-  <si>
     <t>PEREZ MARES RAFAEL</t>
   </si>
   <si>
@@ -269,9 +263,6 @@
     <t>MENDEZ</t>
   </si>
   <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -320,9 +311,6 @@
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>DE GANTE</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -389,9 +377,6 @@
     <t>PAZ AIDE</t>
   </si>
   <si>
-    <t>YARETZI VALERIA</t>
-  </si>
-  <si>
     <t>JESUS MANUEL</t>
   </si>
   <si>
@@ -429,9 +414,6 @@
   </si>
   <si>
     <t>AMY</t>
-  </si>
-  <si>
-    <t>MARIA DEL PILAR</t>
   </si>
   <si>
     <t>RAFAEL</t>
@@ -835,7 +817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y36"/>
+  <dimension ref="A1:Y34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -1348,22 +1330,22 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D9">
         <v>-1</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H9">
         <v>-1</v>
@@ -1402,22 +1384,22 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1425,22 +1407,22 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10">
         <v>-1</v>
       </c>
       <c r="E10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H10">
         <v>-1</v>
@@ -1479,22 +1461,22 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1502,19 +1484,19 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <v>-1</v>
       </c>
       <c r="E11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11">
         <v>10</v>
@@ -1556,19 +1538,19 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1588,10 +1570,10 @@
         <v>-1</v>
       </c>
       <c r="E12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>10</v>
@@ -1642,10 +1624,10 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1659,13 +1641,13 @@
         <v>10</v>
       </c>
       <c r="C13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D13">
         <v>-1</v>
       </c>
       <c r="E13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13">
         <v>10</v>
@@ -1713,13 +1695,13 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -1733,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14">
         <v>7</v>
@@ -1742,13 +1724,13 @@
         <v>-1</v>
       </c>
       <c r="E14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -1787,7 +1769,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>7</v>
@@ -1796,13 +1778,13 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1810,22 +1792,22 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D15">
         <v>-1</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H15">
         <v>-1</v>
@@ -1864,22 +1846,22 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1887,22 +1869,22 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <v>-1</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F16">
         <v>10</v>
       </c>
       <c r="G16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -1941,22 +1923,22 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1976,10 +1958,10 @@
         <v>8</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G17">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H17">
         <v>-1</v>
@@ -2030,10 +2012,10 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2041,76 +2023,76 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D18">
         <v>-1</v>
       </c>
       <c r="E18">
+        <v>10</v>
+      </c>
+      <c r="F18">
+        <v>10</v>
+      </c>
+      <c r="G18">
+        <v>10</v>
+      </c>
+      <c r="H18">
+        <v>-1</v>
+      </c>
+      <c r="I18">
+        <v>-1</v>
+      </c>
+      <c r="J18">
+        <v>-1</v>
+      </c>
+      <c r="K18">
+        <v>-1</v>
+      </c>
+      <c r="L18">
+        <v>-1</v>
+      </c>
+      <c r="M18">
+        <v>-1</v>
+      </c>
+      <c r="N18">
+        <v>-1</v>
+      </c>
+      <c r="O18">
+        <v>-1</v>
+      </c>
+      <c r="P18">
+        <v>-1</v>
+      </c>
+      <c r="Q18">
+        <v>-1</v>
+      </c>
+      <c r="R18">
+        <v>-1</v>
+      </c>
+      <c r="S18">
+        <v>-1</v>
+      </c>
+      <c r="T18">
+        <v>10</v>
+      </c>
+      <c r="U18">
         <v>8</v>
       </c>
-      <c r="F18">
-        <v>7</v>
-      </c>
-      <c r="G18">
-        <v>9</v>
-      </c>
-      <c r="H18">
-        <v>-1</v>
-      </c>
-      <c r="I18">
-        <v>-1</v>
-      </c>
-      <c r="J18">
-        <v>-1</v>
-      </c>
-      <c r="K18">
-        <v>-1</v>
-      </c>
-      <c r="L18">
-        <v>-1</v>
-      </c>
-      <c r="M18">
-        <v>-1</v>
-      </c>
-      <c r="N18">
-        <v>-1</v>
-      </c>
-      <c r="O18">
-        <v>-1</v>
-      </c>
-      <c r="P18">
-        <v>-1</v>
-      </c>
-      <c r="Q18">
-        <v>-1</v>
-      </c>
-      <c r="R18">
-        <v>-1</v>
-      </c>
-      <c r="S18">
-        <v>-1</v>
-      </c>
-      <c r="T18">
-        <v>9</v>
-      </c>
-      <c r="U18">
-        <v>6</v>
-      </c>
       <c r="V18">
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y18">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2121,17 +2103,17 @@
         <v>10</v>
       </c>
       <c r="C19">
+        <v>6</v>
+      </c>
+      <c r="D19">
+        <v>-1</v>
+      </c>
+      <c r="E19">
+        <v>10</v>
+      </c>
+      <c r="F19">
         <v>8</v>
       </c>
-      <c r="D19">
-        <v>-1</v>
-      </c>
-      <c r="E19">
-        <v>10</v>
-      </c>
-      <c r="F19">
-        <v>10</v>
-      </c>
       <c r="G19">
         <v>10</v>
       </c>
@@ -2175,16 +2157,16 @@
         <v>10</v>
       </c>
       <c r="U19">
+        <v>6</v>
+      </c>
+      <c r="V19">
+        <v>-1</v>
+      </c>
+      <c r="W19">
+        <v>10</v>
+      </c>
+      <c r="X19">
         <v>8</v>
-      </c>
-      <c r="V19">
-        <v>-1</v>
-      </c>
-      <c r="W19">
-        <v>10</v>
-      </c>
-      <c r="X19">
-        <v>10</v>
       </c>
       <c r="Y19">
         <v>10</v>
@@ -2198,7 +2180,7 @@
         <v>10</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D20">
         <v>-1</v>
@@ -2207,7 +2189,7 @@
         <v>10</v>
       </c>
       <c r="F20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>10</v>
@@ -2252,7 +2234,7 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -2261,7 +2243,7 @@
         <v>10</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2275,19 +2257,19 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D21">
         <v>-1</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F21">
         <v>10</v>
       </c>
       <c r="G21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H21">
         <v>-1</v>
@@ -2329,19 +2311,19 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2349,22 +2331,22 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D22">
         <v>-1</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H22">
         <v>-1</v>
@@ -2403,22 +2385,22 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2426,22 +2408,22 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C23">
+        <v>6</v>
+      </c>
+      <c r="D23">
+        <v>-1</v>
+      </c>
+      <c r="E23">
         <v>8</v>
       </c>
-      <c r="D23">
-        <v>-1</v>
-      </c>
-      <c r="E23">
-        <v>9</v>
-      </c>
       <c r="F23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H23">
         <v>-1</v>
@@ -2480,22 +2462,22 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U23">
+        <v>6</v>
+      </c>
+      <c r="V23">
+        <v>-1</v>
+      </c>
+      <c r="W23">
         <v>8</v>
       </c>
-      <c r="V23">
-        <v>-1</v>
-      </c>
-      <c r="W23">
-        <v>9</v>
-      </c>
       <c r="X23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2503,7 +2485,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C24">
         <v>6</v>
@@ -2512,14 +2494,14 @@
         <v>-1</v>
       </c>
       <c r="E24">
+        <v>9</v>
+      </c>
+      <c r="F24">
+        <v>9</v>
+      </c>
+      <c r="G24">
         <v>8</v>
       </c>
-      <c r="F24">
-        <v>9</v>
-      </c>
-      <c r="G24">
-        <v>9</v>
-      </c>
       <c r="H24">
         <v>-1</v>
       </c>
@@ -2557,7 +2539,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U24">
         <v>6</v>
@@ -2566,13 +2548,13 @@
         <v>-1</v>
       </c>
       <c r="W24">
+        <v>9</v>
+      </c>
+      <c r="X24">
+        <v>9</v>
+      </c>
+      <c r="Y24">
         <v>8</v>
-      </c>
-      <c r="X24">
-        <v>9</v>
-      </c>
-      <c r="Y24">
-        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2580,76 +2562,76 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D25">
         <v>-1</v>
       </c>
       <c r="E25">
+        <v>9</v>
+      </c>
+      <c r="F25">
+        <v>10</v>
+      </c>
+      <c r="G25">
+        <v>9</v>
+      </c>
+      <c r="H25">
+        <v>-1</v>
+      </c>
+      <c r="I25">
+        <v>-1</v>
+      </c>
+      <c r="J25">
+        <v>-1</v>
+      </c>
+      <c r="K25">
+        <v>-1</v>
+      </c>
+      <c r="L25">
+        <v>-1</v>
+      </c>
+      <c r="M25">
+        <v>-1</v>
+      </c>
+      <c r="N25">
+        <v>-1</v>
+      </c>
+      <c r="O25">
+        <v>-1</v>
+      </c>
+      <c r="P25">
+        <v>-1</v>
+      </c>
+      <c r="Q25">
+        <v>-1</v>
+      </c>
+      <c r="R25">
+        <v>-1</v>
+      </c>
+      <c r="S25">
+        <v>-1</v>
+      </c>
+      <c r="T25">
+        <v>10</v>
+      </c>
+      <c r="U25">
         <v>8</v>
       </c>
-      <c r="F25">
-        <v>9</v>
-      </c>
-      <c r="G25">
-        <v>10</v>
-      </c>
-      <c r="H25">
-        <v>-1</v>
-      </c>
-      <c r="I25">
-        <v>-1</v>
-      </c>
-      <c r="J25">
-        <v>-1</v>
-      </c>
-      <c r="K25">
-        <v>-1</v>
-      </c>
-      <c r="L25">
-        <v>-1</v>
-      </c>
-      <c r="M25">
-        <v>-1</v>
-      </c>
-      <c r="N25">
-        <v>-1</v>
-      </c>
-      <c r="O25">
-        <v>-1</v>
-      </c>
-      <c r="P25">
-        <v>-1</v>
-      </c>
-      <c r="Q25">
-        <v>-1</v>
-      </c>
-      <c r="R25">
-        <v>-1</v>
-      </c>
-      <c r="S25">
-        <v>-1</v>
-      </c>
-      <c r="T25">
-        <v>9</v>
-      </c>
-      <c r="U25">
-        <v>6</v>
-      </c>
       <c r="V25">
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2660,19 +2642,19 @@
         <v>10</v>
       </c>
       <c r="C26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D26">
         <v>-1</v>
       </c>
       <c r="E26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F26">
         <v>9</v>
       </c>
       <c r="G26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H26">
         <v>-1</v>
@@ -2714,19 +2696,19 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X26">
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2737,19 +2719,19 @@
         <v>10</v>
       </c>
       <c r="C27">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D27">
         <v>-1</v>
       </c>
       <c r="E27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H27">
         <v>-1</v>
@@ -2791,19 +2773,19 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V27">
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2820,10 +2802,10 @@
         <v>-1</v>
       </c>
       <c r="E28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G28">
         <v>10</v>
@@ -2874,10 +2856,10 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y28">
         <v>10</v>
@@ -2891,19 +2873,19 @@
         <v>10</v>
       </c>
       <c r="C29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D29">
         <v>-1</v>
       </c>
       <c r="E29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H29">
         <v>-1</v>
@@ -2945,19 +2927,19 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2965,10 +2947,10 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <v>-1</v>
@@ -2977,7 +2959,7 @@
         <v>9</v>
       </c>
       <c r="F30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G30">
         <v>10</v>
@@ -3019,10 +3001,10 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V30">
         <v>-1</v>
@@ -3031,7 +3013,7 @@
         <v>9</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>10</v>
@@ -3045,19 +3027,19 @@
         <v>10</v>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D31">
         <v>-1</v>
       </c>
       <c r="E31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F31">
         <v>10</v>
       </c>
       <c r="G31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H31">
         <v>-1</v>
@@ -3099,19 +3081,19 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V31">
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X31">
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3119,10 +3101,10 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D32">
         <v>-1</v>
@@ -3131,7 +3113,7 @@
         <v>9</v>
       </c>
       <c r="F32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G32">
         <v>10</v>
@@ -3173,10 +3155,10 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V32">
         <v>-1</v>
@@ -3185,7 +3167,7 @@
         <v>9</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -3196,22 +3178,22 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C33">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D33">
         <v>-1</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H33">
         <v>-1</v>
@@ -3250,22 +3232,22 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V33">
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3273,64 +3255,64 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C34">
+        <v>5</v>
+      </c>
+      <c r="D34">
+        <v>-1</v>
+      </c>
+      <c r="E34">
+        <v>9</v>
+      </c>
+      <c r="F34">
+        <v>6</v>
+      </c>
+      <c r="G34">
+        <v>10</v>
+      </c>
+      <c r="H34">
+        <v>-1</v>
+      </c>
+      <c r="I34">
+        <v>-1</v>
+      </c>
+      <c r="J34">
+        <v>-1</v>
+      </c>
+      <c r="K34">
+        <v>-1</v>
+      </c>
+      <c r="L34">
+        <v>-1</v>
+      </c>
+      <c r="M34">
+        <v>-1</v>
+      </c>
+      <c r="N34">
+        <v>-1</v>
+      </c>
+      <c r="O34">
+        <v>-1</v>
+      </c>
+      <c r="P34">
+        <v>-1</v>
+      </c>
+      <c r="Q34">
+        <v>-1</v>
+      </c>
+      <c r="R34">
+        <v>-1</v>
+      </c>
+      <c r="S34">
+        <v>-1</v>
+      </c>
+      <c r="T34">
         <v>8</v>
       </c>
-      <c r="D34">
-        <v>-1</v>
-      </c>
-      <c r="E34">
-        <v>9</v>
-      </c>
-      <c r="F34">
-        <v>10</v>
-      </c>
-      <c r="G34">
-        <v>10</v>
-      </c>
-      <c r="H34">
-        <v>-1</v>
-      </c>
-      <c r="I34">
-        <v>-1</v>
-      </c>
-      <c r="J34">
-        <v>-1</v>
-      </c>
-      <c r="K34">
-        <v>-1</v>
-      </c>
-      <c r="L34">
-        <v>-1</v>
-      </c>
-      <c r="M34">
-        <v>-1</v>
-      </c>
-      <c r="N34">
-        <v>-1</v>
-      </c>
-      <c r="O34">
-        <v>-1</v>
-      </c>
-      <c r="P34">
-        <v>-1</v>
-      </c>
-      <c r="Q34">
-        <v>-1</v>
-      </c>
-      <c r="R34">
-        <v>-1</v>
-      </c>
-      <c r="S34">
-        <v>-1</v>
-      </c>
-      <c r="T34">
-        <v>10</v>
-      </c>
       <c r="U34">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V34">
         <v>-1</v>
@@ -3339,163 +3321,9 @@
         <v>9</v>
       </c>
       <c r="X34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y34">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25">
-      <c r="A35" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35">
-        <v>8</v>
-      </c>
-      <c r="C35">
-        <v>5</v>
-      </c>
-      <c r="D35">
-        <v>-1</v>
-      </c>
-      <c r="E35">
-        <v>9</v>
-      </c>
-      <c r="F35">
-        <v>8</v>
-      </c>
-      <c r="G35">
-        <v>8</v>
-      </c>
-      <c r="H35">
-        <v>-1</v>
-      </c>
-      <c r="I35">
-        <v>-1</v>
-      </c>
-      <c r="J35">
-        <v>-1</v>
-      </c>
-      <c r="K35">
-        <v>-1</v>
-      </c>
-      <c r="L35">
-        <v>-1</v>
-      </c>
-      <c r="M35">
-        <v>-1</v>
-      </c>
-      <c r="N35">
-        <v>-1</v>
-      </c>
-      <c r="O35">
-        <v>-1</v>
-      </c>
-      <c r="P35">
-        <v>-1</v>
-      </c>
-      <c r="Q35">
-        <v>-1</v>
-      </c>
-      <c r="R35">
-        <v>-1</v>
-      </c>
-      <c r="S35">
-        <v>-1</v>
-      </c>
-      <c r="T35">
-        <v>8</v>
-      </c>
-      <c r="U35">
-        <v>5</v>
-      </c>
-      <c r="V35">
-        <v>-1</v>
-      </c>
-      <c r="W35">
-        <v>9</v>
-      </c>
-      <c r="X35">
-        <v>8</v>
-      </c>
-      <c r="Y35">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:25">
-      <c r="A36" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36">
-        <v>8</v>
-      </c>
-      <c r="C36">
-        <v>5</v>
-      </c>
-      <c r="D36">
-        <v>-1</v>
-      </c>
-      <c r="E36">
-        <v>9</v>
-      </c>
-      <c r="F36">
-        <v>6</v>
-      </c>
-      <c r="G36">
-        <v>10</v>
-      </c>
-      <c r="H36">
-        <v>-1</v>
-      </c>
-      <c r="I36">
-        <v>-1</v>
-      </c>
-      <c r="J36">
-        <v>-1</v>
-      </c>
-      <c r="K36">
-        <v>-1</v>
-      </c>
-      <c r="L36">
-        <v>-1</v>
-      </c>
-      <c r="M36">
-        <v>-1</v>
-      </c>
-      <c r="N36">
-        <v>-1</v>
-      </c>
-      <c r="O36">
-        <v>-1</v>
-      </c>
-      <c r="P36">
-        <v>-1</v>
-      </c>
-      <c r="Q36">
-        <v>-1</v>
-      </c>
-      <c r="R36">
-        <v>-1</v>
-      </c>
-      <c r="S36">
-        <v>-1</v>
-      </c>
-      <c r="T36">
-        <v>8</v>
-      </c>
-      <c r="U36">
-        <v>5</v>
-      </c>
-      <c r="V36">
-        <v>-1</v>
-      </c>
-      <c r="W36">
-        <v>9</v>
-      </c>
-      <c r="X36">
-        <v>6</v>
-      </c>
-      <c r="Y36">
         <v>10</v>
       </c>
     </row>
@@ -3512,37 +3340,40 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3553,51 +3384,60 @@
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="L2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="P2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="R2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:19">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -3608,7 +3448,7 @@
         <v>100</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -3626,7 +3466,7 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <v>100</v>
@@ -3644,10 +3484,19 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4">
+        <v>100</v>
+      </c>
+      <c r="S4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -3658,7 +3507,7 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>100</v>
@@ -3676,7 +3525,7 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K5">
         <v>100</v>
@@ -3694,10 +3543,19 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>100</v>
+      </c>
+      <c r="R5">
+        <v>100</v>
+      </c>
+      <c r="S5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -3708,7 +3566,7 @@
         <v>100</v>
       </c>
       <c r="D6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>100</v>
@@ -3726,7 +3584,7 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <v>100</v>
@@ -3744,10 +3602,19 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>100</v>
+      </c>
+      <c r="R6">
+        <v>100</v>
+      </c>
+      <c r="S6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -3758,7 +3625,7 @@
         <v>100</v>
       </c>
       <c r="D7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -3776,7 +3643,7 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <v>100</v>
@@ -3794,10 +3661,19 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>100</v>
+      </c>
+      <c r="R7">
+        <v>100</v>
+      </c>
+      <c r="S7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -3808,7 +3684,7 @@
         <v>92</v>
       </c>
       <c r="D8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>100</v>
@@ -3820,13 +3696,13 @@
         <v>100</v>
       </c>
       <c r="H8">
+        <v>100</v>
+      </c>
+      <c r="I8">
         <v>92</v>
       </c>
-      <c r="I8">
-        <v>100</v>
-      </c>
       <c r="J8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <v>100</v>
@@ -3835,69 +3711,87 @@
         <v>100</v>
       </c>
       <c r="M8">
+        <v>100</v>
+      </c>
+      <c r="N8">
+        <v>100</v>
+      </c>
+      <c r="O8">
         <v>92</v>
       </c>
-      <c r="N8">
-        <v>100</v>
-      </c>
-      <c r="O8">
-        <v>100</v>
-      </c>
       <c r="P8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>100</v>
+      </c>
+      <c r="R8">
+        <v>100</v>
+      </c>
+      <c r="S8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9">
+        <v>100</v>
+      </c>
+      <c r="R9">
+        <v>100</v>
+      </c>
+      <c r="S9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -3905,10 +3799,10 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>100</v>
@@ -3920,13 +3814,13 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="I10">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K10">
         <v>100</v>
@@ -3935,19 +3829,28 @@
         <v>100</v>
       </c>
       <c r="M10">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="N10">
         <v>100</v>
       </c>
       <c r="O10">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P10">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>100</v>
+      </c>
+      <c r="R10">
+        <v>100</v>
+      </c>
+      <c r="S10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -3955,10 +3858,10 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>100</v>
@@ -3970,13 +3873,13 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I11">
         <v>100</v>
       </c>
       <c r="J11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -3985,7 +3888,7 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N11">
         <v>100</v>
@@ -3994,10 +3897,19 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>100</v>
+      </c>
+      <c r="R11">
+        <v>100</v>
+      </c>
+      <c r="S11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -4008,7 +3920,7 @@
         <v>100</v>
       </c>
       <c r="D12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>100</v>
@@ -4026,7 +3938,7 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <v>100</v>
@@ -4044,21 +3956,30 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>100</v>
+      </c>
+      <c r="R12">
+        <v>100</v>
+      </c>
+      <c r="S12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B13">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C13">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>100</v>
@@ -4070,13 +3991,13 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I13">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -4088,27 +4009,36 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O13">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
+        <v>100</v>
+      </c>
+      <c r="S13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B14">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C14">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>100</v>
@@ -4117,25 +4047,25 @@
         <v>100</v>
       </c>
       <c r="G14">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H14">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I14">
         <v>100</v>
       </c>
       <c r="J14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K14">
         <v>100</v>
       </c>
       <c r="L14">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="M14">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N14">
         <v>100</v>
@@ -4144,10 +4074,19 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>100</v>
+      </c>
+      <c r="R14">
+        <v>100</v>
+      </c>
+      <c r="S14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -4158,7 +4097,7 @@
         <v>100</v>
       </c>
       <c r="D15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>100</v>
@@ -4176,7 +4115,7 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -4194,10 +4133,19 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
+        <v>100</v>
+      </c>
+      <c r="S15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
       <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
@@ -4208,7 +4156,7 @@
         <v>100</v>
       </c>
       <c r="D16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>100</v>
@@ -4217,7 +4165,7 @@
         <v>100</v>
       </c>
       <c r="G16">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H16">
         <v>100</v>
@@ -4226,7 +4174,7 @@
         <v>100</v>
       </c>
       <c r="J16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K16">
         <v>100</v>
@@ -4235,7 +4183,7 @@
         <v>100</v>
       </c>
       <c r="M16">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N16">
         <v>100</v>
@@ -4244,42 +4192,51 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
+        <v>100</v>
+      </c>
+      <c r="S16">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C17">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>100</v>
       </c>
       <c r="F17">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G17">
         <v>100</v>
       </c>
       <c r="H17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I17">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="J17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -4288,27 +4245,36 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O17">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="P17">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>100</v>
+      </c>
+      <c r="R17">
+        <v>100</v>
+      </c>
+      <c r="S17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B18">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C18">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>100</v>
@@ -4317,25 +4283,25 @@
         <v>100</v>
       </c>
       <c r="G18">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H18">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="I18">
         <v>100</v>
       </c>
       <c r="J18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K18">
         <v>100</v>
       </c>
       <c r="L18">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="M18">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="N18">
         <v>100</v>
@@ -4344,10 +4310,19 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
+        <v>100</v>
+      </c>
+      <c r="S18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
@@ -4355,10 +4330,10 @@
         <v>100</v>
       </c>
       <c r="C19">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>100</v>
@@ -4373,10 +4348,10 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K19">
         <v>100</v>
@@ -4391,13 +4366,22 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P19">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>100</v>
+      </c>
+      <c r="R19">
+        <v>100</v>
+      </c>
+      <c r="S19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
@@ -4405,10 +4389,10 @@
         <v>100</v>
       </c>
       <c r="C20">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>100</v>
@@ -4420,13 +4404,13 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I20">
         <v>100</v>
       </c>
       <c r="J20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K20">
         <v>100</v>
@@ -4435,7 +4419,7 @@
         <v>100</v>
       </c>
       <c r="M20">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N20">
         <v>100</v>
@@ -4444,10 +4428,19 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>100</v>
+      </c>
+      <c r="R20">
+        <v>100</v>
+      </c>
+      <c r="S20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" s="1" t="s">
         <v>29</v>
       </c>
@@ -4458,7 +4451,7 @@
         <v>100</v>
       </c>
       <c r="D21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>100</v>
@@ -4476,7 +4469,7 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K21">
         <v>100</v>
@@ -4494,60 +4487,78 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
+        <v>100</v>
+      </c>
+      <c r="S21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:16">
+      <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="R22">
+        <v>100</v>
+      </c>
+      <c r="S22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
@@ -4558,7 +4569,7 @@
         <v>100</v>
       </c>
       <c r="D23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>100</v>
@@ -4576,7 +4587,7 @@
         <v>100</v>
       </c>
       <c r="J23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K23">
         <v>100</v>
@@ -4594,10 +4605,19 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>100</v>
+      </c>
+      <c r="R23">
+        <v>100</v>
+      </c>
+      <c r="S23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
       <c r="A24" s="1" t="s">
         <v>32</v>
       </c>
@@ -4605,10 +4625,10 @@
         <v>100</v>
       </c>
       <c r="C24">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>100</v>
@@ -4623,10 +4643,10 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K24">
         <v>100</v>
@@ -4641,13 +4661,22 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P24">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>100</v>
+      </c>
+      <c r="R24">
+        <v>100</v>
+      </c>
+      <c r="S24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
       <c r="A25" s="1" t="s">
         <v>33</v>
       </c>
@@ -4658,7 +4687,7 @@
         <v>100</v>
       </c>
       <c r="D25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <v>100</v>
@@ -4676,7 +4705,7 @@
         <v>100</v>
       </c>
       <c r="J25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K25">
         <v>100</v>
@@ -4694,10 +4723,19 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>100</v>
+      </c>
+      <c r="R25">
+        <v>100</v>
+      </c>
+      <c r="S25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
       <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
@@ -4708,7 +4746,7 @@
         <v>96</v>
       </c>
       <c r="D26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E26">
         <v>100</v>
@@ -4720,13 +4758,13 @@
         <v>100</v>
       </c>
       <c r="H26">
+        <v>100</v>
+      </c>
+      <c r="I26">
         <v>96</v>
       </c>
-      <c r="I26">
-        <v>100</v>
-      </c>
       <c r="J26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K26">
         <v>100</v>
@@ -4735,19 +4773,28 @@
         <v>100</v>
       </c>
       <c r="M26">
+        <v>100</v>
+      </c>
+      <c r="N26">
+        <v>100</v>
+      </c>
+      <c r="O26">
         <v>96</v>
       </c>
-      <c r="N26">
-        <v>100</v>
-      </c>
-      <c r="O26">
-        <v>100</v>
-      </c>
       <c r="P26">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>100</v>
+      </c>
+      <c r="R26">
+        <v>100</v>
+      </c>
+      <c r="S26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
       <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
@@ -4755,10 +4802,10 @@
         <v>100</v>
       </c>
       <c r="C27">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <v>100</v>
@@ -4773,10 +4820,10 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K27">
         <v>100</v>
@@ -4791,13 +4838,22 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P27">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>100</v>
+      </c>
+      <c r="R27">
+        <v>100</v>
+      </c>
+      <c r="S27">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
       <c r="A28" s="1" t="s">
         <v>36</v>
       </c>
@@ -4805,10 +4861,10 @@
         <v>100</v>
       </c>
       <c r="C28">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>100</v>
@@ -4820,13 +4876,13 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I28">
         <v>100</v>
       </c>
       <c r="J28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K28">
         <v>100</v>
@@ -4835,7 +4891,7 @@
         <v>100</v>
       </c>
       <c r="M28">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N28">
         <v>100</v>
@@ -4844,10 +4900,19 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>100</v>
+      </c>
+      <c r="R28">
+        <v>100</v>
+      </c>
+      <c r="S28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
@@ -4858,7 +4923,7 @@
         <v>96</v>
       </c>
       <c r="D29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E29">
         <v>100</v>
@@ -4870,13 +4935,13 @@
         <v>100</v>
       </c>
       <c r="H29">
+        <v>100</v>
+      </c>
+      <c r="I29">
         <v>96</v>
       </c>
-      <c r="I29">
-        <v>100</v>
-      </c>
       <c r="J29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K29">
         <v>100</v>
@@ -4885,19 +4950,28 @@
         <v>100</v>
       </c>
       <c r="M29">
+        <v>100</v>
+      </c>
+      <c r="N29">
+        <v>100</v>
+      </c>
+      <c r="O29">
         <v>96</v>
       </c>
-      <c r="N29">
-        <v>100</v>
-      </c>
-      <c r="O29">
-        <v>100</v>
-      </c>
       <c r="P29">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>100</v>
+      </c>
+      <c r="R29">
+        <v>100</v>
+      </c>
+      <c r="S29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
       <c r="A30" s="1" t="s">
         <v>38</v>
       </c>
@@ -4908,7 +4982,7 @@
         <v>100</v>
       </c>
       <c r="D30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>100</v>
@@ -4926,7 +5000,7 @@
         <v>100</v>
       </c>
       <c r="J30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K30">
         <v>100</v>
@@ -4944,10 +5018,19 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>100</v>
+      </c>
+      <c r="R30">
+        <v>100</v>
+      </c>
+      <c r="S30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
       <c r="A31" s="1" t="s">
         <v>39</v>
       </c>
@@ -4955,10 +5038,10 @@
         <v>100</v>
       </c>
       <c r="C31">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D31">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <v>100</v>
@@ -4970,13 +5053,13 @@
         <v>100</v>
       </c>
       <c r="H31">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I31">
         <v>100</v>
       </c>
       <c r="J31">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K31">
         <v>100</v>
@@ -4985,7 +5068,7 @@
         <v>100</v>
       </c>
       <c r="M31">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N31">
         <v>100</v>
@@ -4994,10 +5077,19 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>100</v>
+      </c>
+      <c r="R31">
+        <v>100</v>
+      </c>
+      <c r="S31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
@@ -5008,7 +5100,7 @@
         <v>100</v>
       </c>
       <c r="D32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>100</v>
@@ -5026,7 +5118,7 @@
         <v>100</v>
       </c>
       <c r="J32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K32">
         <v>100</v>
@@ -5044,10 +5136,19 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>100</v>
+      </c>
+      <c r="R32">
+        <v>100</v>
+      </c>
+      <c r="S32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
       <c r="A33" s="1" t="s">
         <v>41</v>
       </c>
@@ -5055,10 +5156,10 @@
         <v>100</v>
       </c>
       <c r="C33">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D33">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>100</v>
@@ -5073,10 +5174,10 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J33">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K33">
         <v>100</v>
@@ -5091,13 +5192,22 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P33">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>100</v>
+      </c>
+      <c r="R33">
+        <v>100</v>
+      </c>
+      <c r="S33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34" s="1" t="s">
         <v>42</v>
       </c>
@@ -5108,7 +5218,7 @@
         <v>100</v>
       </c>
       <c r="D34">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E34">
         <v>100</v>
@@ -5126,7 +5236,7 @@
         <v>100</v>
       </c>
       <c r="J34">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K34">
         <v>100</v>
@@ -5144,114 +5254,23 @@
         <v>100</v>
       </c>
       <c r="P34">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16">
-      <c r="A35" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35">
-        <v>100</v>
-      </c>
-      <c r="C35">
-        <v>96</v>
-      </c>
-      <c r="D35">
-        <v>100</v>
-      </c>
-      <c r="E35">
-        <v>100</v>
-      </c>
-      <c r="F35">
-        <v>100</v>
-      </c>
-      <c r="G35">
-        <v>100</v>
-      </c>
-      <c r="H35">
-        <v>96</v>
-      </c>
-      <c r="I35">
-        <v>100</v>
-      </c>
-      <c r="J35">
-        <v>100</v>
-      </c>
-      <c r="K35">
-        <v>100</v>
-      </c>
-      <c r="L35">
-        <v>100</v>
-      </c>
-      <c r="M35">
-        <v>96</v>
-      </c>
-      <c r="N35">
-        <v>100</v>
-      </c>
-      <c r="O35">
-        <v>100</v>
-      </c>
-      <c r="P35">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16">
-      <c r="A36" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36">
-        <v>100</v>
-      </c>
-      <c r="C36">
-        <v>100</v>
-      </c>
-      <c r="D36">
-        <v>100</v>
-      </c>
-      <c r="E36">
-        <v>100</v>
-      </c>
-      <c r="F36">
-        <v>100</v>
-      </c>
-      <c r="G36">
-        <v>100</v>
-      </c>
-      <c r="H36">
-        <v>100</v>
-      </c>
-      <c r="I36">
-        <v>100</v>
-      </c>
-      <c r="J36">
-        <v>100</v>
-      </c>
-      <c r="K36">
-        <v>100</v>
-      </c>
-      <c r="L36">
-        <v>100</v>
-      </c>
-      <c r="M36">
-        <v>100</v>
-      </c>
-      <c r="N36">
-        <v>100</v>
-      </c>
-      <c r="O36">
-        <v>100</v>
-      </c>
-      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>100</v>
+      </c>
+      <c r="R34">
+        <v>100</v>
+      </c>
+      <c r="S34">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5272,31 +5291,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -5304,7 +5323,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C2">
         <v>33</v>
@@ -5333,7 +5352,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C3">
         <v>33</v>
@@ -5365,7 +5384,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C4">
         <v>33</v>
@@ -5397,7 +5416,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C5">
         <v>33</v>
@@ -5429,7 +5448,7 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C6">
         <v>33</v>
@@ -5461,7 +5480,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C7">
         <v>33</v>
@@ -5495,7 +5514,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5504,16 +5523,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -5527,19 +5546,19 @@
         <v>21330051920215</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -5547,19 +5566,19 @@
         <v>21330051920216</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5567,19 +5586,19 @@
         <v>21330051920033</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5587,107 +5606,107 @@
         <v>21330051920217</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920218</v>
+        <v>21330051920219</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920218</v>
+        <v>21330051920220</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920218</v>
+        <v>21330051920221</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920218</v>
+        <v>21330051920230</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920218</v>
+        <v>21330051920231</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
         <v>100</v>
@@ -5696,690 +5715,450 @@
         <v>123</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920218</v>
+        <v>21330051920232</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920219</v>
+        <v>21330051920233</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920220</v>
+        <v>21330051920042</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920221</v>
+        <v>21330051920044</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920230</v>
+        <v>21330051920235</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920231</v>
+        <v>21330051920236</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920232</v>
+        <v>21330051920239</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920233</v>
+        <v>21330051920049</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920042</v>
+        <v>21330051920244</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920044</v>
+        <v>21330051920246</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920235</v>
+        <v>21330051920247</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920236</v>
+        <v>21330051920248</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E22" t="s">
         <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920239</v>
+        <v>21330051920249</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920049</v>
+        <v>21330051920250</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920241</v>
+        <v>21330051920229</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="D25" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F25" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920241</v>
+        <v>21330051920228</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E26" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F26" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920241</v>
+        <v>21330051920066</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E27" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F27" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920241</v>
+        <v>21330051920227</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D28" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E28" t="s">
         <v>7</v>
       </c>
       <c r="F28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920241</v>
+        <v>21330051920226</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D29" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>21330051920241</v>
+        <v>21330051920224</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="D30" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F30" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>21330051920244</v>
+        <v>21330051920223</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D31" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E31" t="s">
         <v>7</v>
       </c>
       <c r="F31" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920246</v>
+        <v>21330051920222</v>
       </c>
       <c r="B32" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D32" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E32" t="s">
         <v>7</v>
       </c>
       <c r="F32" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920247</v>
-      </c>
-      <c r="B33" t="s">
-        <v>86</v>
-      </c>
-      <c r="C33" t="s">
-        <v>111</v>
-      </c>
-      <c r="D33" t="s">
-        <v>140</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920248</v>
-      </c>
-      <c r="B34" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" t="s">
-        <v>112</v>
-      </c>
-      <c r="D34" t="s">
-        <v>141</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920249</v>
-      </c>
-      <c r="B35" t="s">
-        <v>88</v>
-      </c>
-      <c r="C35" t="s">
-        <v>113</v>
-      </c>
-      <c r="D35" t="s">
-        <v>142</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920250</v>
-      </c>
-      <c r="B36" t="s">
-        <v>89</v>
-      </c>
-      <c r="C36" t="s">
-        <v>114</v>
-      </c>
-      <c r="D36" t="s">
-        <v>143</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920229</v>
-      </c>
-      <c r="B37" t="s">
-        <v>89</v>
-      </c>
-      <c r="C37" t="s">
-        <v>84</v>
-      </c>
-      <c r="D37" t="s">
-        <v>144</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920228</v>
-      </c>
-      <c r="B38" t="s">
-        <v>90</v>
-      </c>
-      <c r="C38" t="s">
-        <v>115</v>
-      </c>
-      <c r="D38" t="s">
-        <v>145</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920066</v>
-      </c>
-      <c r="B39" t="s">
-        <v>91</v>
-      </c>
-      <c r="C39" t="s">
-        <v>110</v>
-      </c>
-      <c r="D39" t="s">
-        <v>146</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920227</v>
-      </c>
-      <c r="B40" t="s">
-        <v>92</v>
-      </c>
-      <c r="C40" t="s">
-        <v>116</v>
-      </c>
-      <c r="D40" t="s">
-        <v>147</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920226</v>
-      </c>
-      <c r="B41" t="s">
-        <v>93</v>
-      </c>
-      <c r="C41" t="s">
-        <v>117</v>
-      </c>
-      <c r="D41" t="s">
-        <v>148</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920224</v>
-      </c>
-      <c r="B42" t="s">
-        <v>94</v>
-      </c>
-      <c r="C42" t="s">
-        <v>101</v>
-      </c>
-      <c r="D42" t="s">
-        <v>149</v>
-      </c>
-      <c r="E42" t="s">
-        <v>7</v>
-      </c>
-      <c r="F42" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920223</v>
-      </c>
-      <c r="B43" t="s">
-        <v>95</v>
-      </c>
-      <c r="C43" t="s">
-        <v>118</v>
-      </c>
-      <c r="D43" t="s">
-        <v>150</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920222</v>
-      </c>
-      <c r="B44" t="s">
-        <v>96</v>
-      </c>
-      <c r="C44" t="s">
-        <v>106</v>
-      </c>
-      <c r="D44" t="s">
-        <v>151</v>
-      </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -6398,22 +6177,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -6424,19 +6203,19 @@
         <v>21330051920250</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6447,19 +6226,19 @@
         <v>21330051920250</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -6470,19 +6249,19 @@
         <v>21330051920223</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6493,19 +6272,19 @@
         <v>21330051920223</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -6516,19 +6295,19 @@
         <v>21330051920222</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6539,19 +6318,19 @@
         <v>21330051920222</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -6562,19 +6341,19 @@
         <v>21330051920215</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -6585,19 +6364,19 @@
         <v>21330051920216</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -6608,19 +6387,19 @@
         <v>21330051920033</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G10">
         <v>-1</v>
@@ -6631,19 +6410,19 @@
         <v>21330051920217</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -6654,19 +6433,19 @@
         <v>21330051920219</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -6677,19 +6456,19 @@
         <v>21330051920220</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -6700,19 +6479,19 @@
         <v>21330051920221</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -6723,19 +6502,19 @@
         <v>21330051920230</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G15">
         <v>-1</v>
@@ -6746,19 +6525,19 @@
         <v>21330051920231</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G16">
         <v>-1</v>
@@ -6769,19 +6548,19 @@
         <v>21330051920232</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G17">
         <v>-1</v>
@@ -6792,19 +6571,19 @@
         <v>21330051920233</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G18">
         <v>-1</v>
@@ -6815,19 +6594,19 @@
         <v>21330051920042</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G19">
         <v>-1</v>
@@ -6838,19 +6617,19 @@
         <v>21330051920044</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G20">
         <v>-1</v>
@@ -6861,19 +6640,19 @@
         <v>21330051920235</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G21">
         <v>-1</v>
@@ -6884,19 +6663,19 @@
         <v>21330051920236</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E22" t="s">
         <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G22">
         <v>-1</v>
@@ -6907,19 +6686,19 @@
         <v>21330051920239</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G23">
         <v>-1</v>
@@ -6930,19 +6709,19 @@
         <v>21330051920049</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G24">
         <v>-1</v>
@@ -6953,19 +6732,19 @@
         <v>21330051920244</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E25" t="s">
         <v>7</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G25">
         <v>-1</v>
@@ -6976,19 +6755,19 @@
         <v>21330051920246</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E26" t="s">
         <v>7</v>
       </c>
       <c r="F26" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G26">
         <v>-1</v>
@@ -6999,19 +6778,19 @@
         <v>21330051920247</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E27" t="s">
         <v>7</v>
       </c>
       <c r="F27" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G27">
         <v>-1</v>
@@ -7022,19 +6801,19 @@
         <v>21330051920248</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E28" t="s">
         <v>7</v>
       </c>
       <c r="F28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G28">
         <v>-1</v>
@@ -7045,19 +6824,19 @@
         <v>21330051920249</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E29" t="s">
         <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G29">
         <v>-1</v>
@@ -7068,19 +6847,19 @@
         <v>21330051920229</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C30" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D30" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E30" t="s">
         <v>7</v>
       </c>
       <c r="F30" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G30">
         <v>-1</v>
@@ -7091,19 +6870,19 @@
         <v>21330051920228</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D31" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E31" t="s">
         <v>7</v>
       </c>
       <c r="F31" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G31">
         <v>-1</v>
@@ -7114,19 +6893,19 @@
         <v>21330051920066</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E32" t="s">
         <v>7</v>
       </c>
       <c r="F32" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G32">
         <v>-1</v>
@@ -7137,19 +6916,19 @@
         <v>21330051920227</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E33" t="s">
         <v>7</v>
       </c>
       <c r="F33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G33">
         <v>-1</v>
@@ -7160,19 +6939,19 @@
         <v>21330051920226</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C34" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D34" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E34" t="s">
         <v>7</v>
       </c>
       <c r="F34" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G34">
         <v>-1</v>
@@ -7183,19 +6962,19 @@
         <v>21330051920224</v>
       </c>
       <c r="B35" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C35" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D35" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E35" t="s">
         <v>7</v>
       </c>
       <c r="F35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G35">
         <v>-1</v>

--- a/grupos/5ARHM - Estadisticos 20231.xlsx
+++ b/grupos/5ARHM - Estadisticos 20231.xlsx
@@ -5326,7 +5326,7 @@
         <v>55</v>
       </c>
       <c r="C2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -5341,7 +5341,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J2" s="2">
         <v>100</v>
@@ -5355,7 +5355,7 @@
         <v>56</v>
       </c>
       <c r="C3">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D3">
         <v>28</v>
@@ -5364,19 +5364,19 @@
         <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>84.8</v>
+        <v>90.3</v>
       </c>
       <c r="G3" s="2">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H3">
         <v>7.4</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2">
-        <v>6.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -5387,7 +5387,7 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D4">
         <v>31</v>
@@ -5396,7 +5396,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -5405,10 +5405,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2">
-        <v>6.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -5419,7 +5419,7 @@
         <v>58</v>
       </c>
       <c r="C5">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D5">
         <v>31</v>
@@ -5428,7 +5428,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -5437,10 +5437,10 @@
         <v>9.6</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>6.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -5451,7 +5451,7 @@
         <v>59</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D6">
         <v>31</v>
@@ -5460,7 +5460,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
@@ -5469,10 +5469,10 @@
         <v>9.4</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>6.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -5483,7 +5483,7 @@
         <v>60</v>
       </c>
       <c r="C7">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D7">
         <v>31</v>
@@ -5492,7 +5492,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
@@ -5501,10 +5501,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>6.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5ARHM - Estadisticos 20231.xlsx
+++ b/grupos/5ARHM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="88">
   <si>
     <t>Materia</t>
   </si>
@@ -215,241 +215,67 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>AHUET</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>DURAND</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>LOMAN</t>
-  </si>
-  <si>
     <t>MADRIGAL</t>
   </si>
   <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
     <t>TEHUINTLE</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
     <t>ZACAMECAHUA</t>
   </si>
   <si>
     <t>ZEPEDA</t>
   </si>
   <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>GRANADOS</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>GALVAN</t>
-  </si>
-  <si>
     <t>MARES</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>LETICIA ANETTE</t>
-  </si>
-  <si>
-    <t>ERANDI</t>
-  </si>
-  <si>
-    <t>GUADALUPE JOSELYNE</t>
-  </si>
-  <si>
-    <t>PAZ AIDE</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>LAURA EVELYN</t>
-  </si>
-  <si>
-    <t>KARINA</t>
-  </si>
-  <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
-    <t>DIANA ITZEL</t>
-  </si>
-  <si>
     <t>ALONDRA VANNESSA</t>
   </si>
   <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>NOHEMI</t>
-  </si>
-  <si>
-    <t>ARANZA DANAE</t>
-  </si>
-  <si>
     <t>LIZBETH JOSELYN</t>
   </si>
   <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
     <t>AMERICA PAOLA</t>
   </si>
   <si>
-    <t>AMY</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>CITLALI</t>
-  </si>
-  <si>
-    <t>ALMA PATRICIA</t>
-  </si>
-  <si>
     <t>LUCERO</t>
   </si>
   <si>
     <t>GETSEMANI GUADALUPE</t>
-  </si>
-  <si>
-    <t>NESTOR JOSUE</t>
-  </si>
-  <si>
-    <t>DIANA GUADALUPE</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>JARITZA</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>MARIELA</t>
   </si>
   <si>
     <t>HARUMI</t>
@@ -951,7 +777,7 @@
         <v>10</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -963,7 +789,7 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -972,13 +798,13 @@
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1005,7 +831,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -1028,7 +854,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -1040,7 +866,7 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1049,13 +875,13 @@
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1082,7 +908,7 @@
         <v>7</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -1105,7 +931,7 @@
         <v>9</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>9</v>
@@ -1117,7 +943,7 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1126,13 +952,13 @@
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1159,7 +985,7 @@
         <v>9</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1182,7 +1008,7 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E7">
         <v>9</v>
@@ -1194,7 +1020,7 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1203,13 +1029,13 @@
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1230,19 +1056,19 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U7">
         <v>7</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>9</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1259,7 +1085,7 @@
         <v>8</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E8">
         <v>9</v>
@@ -1271,7 +1097,7 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1280,13 +1106,13 @@
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1313,7 +1139,7 @@
         <v>8</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1336,7 +1162,7 @@
         <v>6</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1348,7 +1174,7 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1357,13 +1183,13 @@
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1390,13 +1216,13 @@
         <v>6</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1413,7 +1239,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1425,7 +1251,7 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1434,13 +1260,13 @@
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1461,13 +1287,13 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U10">
         <v>7</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1490,7 +1316,7 @@
         <v>8</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1502,7 +1328,7 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1511,13 +1337,13 @@
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1544,7 +1370,7 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -1567,7 +1393,7 @@
         <v>8</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E12">
         <v>9</v>
@@ -1579,7 +1405,7 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1588,13 +1414,13 @@
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1621,7 +1447,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1644,7 +1470,7 @@
         <v>7</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E13">
         <v>10</v>
@@ -1656,7 +1482,7 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1665,13 +1491,13 @@
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1698,7 +1524,7 @@
         <v>7</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1721,7 +1547,7 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E14">
         <v>9</v>
@@ -1733,7 +1559,7 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1742,13 +1568,13 @@
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1769,22 +1595,22 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>7</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>9</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1798,7 +1624,7 @@
         <v>9</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>10</v>
@@ -1810,7 +1636,7 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1819,13 +1645,13 @@
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1852,7 +1678,7 @@
         <v>9</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>10</v>
@@ -1875,7 +1701,7 @@
         <v>6</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <v>8</v>
@@ -1887,7 +1713,7 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -1896,13 +1722,13 @@
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1929,16 +1755,16 @@
         <v>6</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1952,7 +1778,7 @@
         <v>6</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E17">
         <v>8</v>
@@ -1964,7 +1790,7 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -1973,13 +1799,13 @@
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2000,22 +1826,22 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U17">
         <v>6</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2029,7 +1855,7 @@
         <v>8</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E18">
         <v>10</v>
@@ -2041,7 +1867,7 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2050,13 +1876,13 @@
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2083,7 +1909,7 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>10</v>
@@ -2106,7 +1932,7 @@
         <v>6</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>10</v>
@@ -2118,7 +1944,7 @@
         <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2127,13 +1953,13 @@
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2160,13 +1986,13 @@
         <v>6</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>10</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>10</v>
@@ -2183,7 +2009,7 @@
         <v>10</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E20">
         <v>10</v>
@@ -2195,7 +2021,7 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2204,13 +2030,13 @@
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2237,7 +2063,7 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>10</v>
@@ -2260,7 +2086,7 @@
         <v>8</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E21">
         <v>9</v>
@@ -2272,7 +2098,7 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2281,13 +2107,13 @@
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2314,7 +2140,7 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2337,7 +2163,7 @@
         <v>6</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E22">
         <v>8</v>
@@ -2349,7 +2175,7 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2358,13 +2184,13 @@
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2385,16 +2211,16 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U22">
         <v>6</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -2414,7 +2240,7 @@
         <v>6</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E23">
         <v>8</v>
@@ -2426,7 +2252,7 @@
         <v>10</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2435,13 +2261,13 @@
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2462,16 +2288,16 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U23">
         <v>6</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>9</v>
@@ -2491,7 +2317,7 @@
         <v>6</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E24">
         <v>9</v>
@@ -2503,7 +2329,7 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2512,13 +2338,13 @@
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2539,13 +2365,13 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>6</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W24">
         <v>9</v>
@@ -2554,7 +2380,7 @@
         <v>9</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2568,7 +2394,7 @@
         <v>8</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E25">
         <v>9</v>
@@ -2580,7 +2406,7 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2589,13 +2415,13 @@
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2622,16 +2448,16 @@
         <v>8</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2645,7 +2471,7 @@
         <v>10</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E26">
         <v>10</v>
@@ -2657,7 +2483,7 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2666,13 +2492,13 @@
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2699,13 +2525,13 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>10</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y26">
         <v>10</v>
@@ -2722,7 +2548,7 @@
         <v>5</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E27">
         <v>10</v>
@@ -2734,7 +2560,7 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -2743,13 +2569,13 @@
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2776,13 +2602,13 @@
         <v>5</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W27">
         <v>10</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y27">
         <v>10</v>
@@ -2799,7 +2625,7 @@
         <v>10</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E28">
         <v>9</v>
@@ -2811,7 +2637,7 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -2820,13 +2646,13 @@
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2853,7 +2679,7 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -2876,7 +2702,7 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E29">
         <v>8</v>
@@ -2888,7 +2714,7 @@
         <v>9</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -2897,13 +2723,13 @@
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2930,16 +2756,16 @@
         <v>7</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2953,7 +2779,7 @@
         <v>7</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E30">
         <v>9</v>
@@ -2965,7 +2791,7 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -2974,13 +2800,13 @@
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3001,19 +2827,19 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U30">
         <v>7</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>9</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y30">
         <v>10</v>
@@ -3030,7 +2856,7 @@
         <v>10</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E31">
         <v>10</v>
@@ -3042,7 +2868,7 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -3051,13 +2877,13 @@
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3084,7 +2910,7 @@
         <v>10</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>10</v>
@@ -3107,7 +2933,7 @@
         <v>8</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E32">
         <v>9</v>
@@ -3119,7 +2945,7 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3128,13 +2954,13 @@
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3161,7 +2987,7 @@
         <v>8</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>9</v>
@@ -3184,7 +3010,7 @@
         <v>5</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E33">
         <v>9</v>
@@ -3196,7 +3022,7 @@
         <v>8</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3205,13 +3031,13 @@
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3232,13 +3058,13 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U33">
         <v>5</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W33">
         <v>9</v>
@@ -3261,7 +3087,7 @@
         <v>5</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E34">
         <v>9</v>
@@ -3273,7 +3099,7 @@
         <v>10</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3282,13 +3108,13 @@
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3315,7 +3141,7 @@
         <v>5</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W34">
         <v>9</v>
@@ -3324,7 +3150,7 @@
         <v>6</v>
       </c>
       <c r="Y34">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3448,7 +3274,7 @@
         <v>100</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -3466,10 +3292,10 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L4">
         <v>100</v>
@@ -3484,10 +3310,10 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -3507,7 +3333,7 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E5">
         <v>100</v>
@@ -3519,13 +3345,13 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I5">
         <v>100</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5">
         <v>100</v>
@@ -3537,13 +3363,13 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -3566,7 +3392,7 @@
         <v>100</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>100</v>
@@ -3584,7 +3410,7 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K6">
         <v>100</v>
@@ -3602,7 +3428,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -3625,7 +3451,7 @@
         <v>100</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -3643,7 +3469,7 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K7">
         <v>100</v>
@@ -3661,7 +3487,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -3684,7 +3510,7 @@
         <v>92</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E8">
         <v>100</v>
@@ -3702,7 +3528,7 @@
         <v>92</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8">
         <v>100</v>
@@ -3720,7 +3546,7 @@
         <v>92</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3743,7 +3569,7 @@
         <v>92</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -3755,13 +3581,13 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I9">
         <v>92</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -3773,13 +3599,13 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O9">
         <v>92</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -3802,7 +3628,7 @@
         <v>96</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E10">
         <v>100</v>
@@ -3820,7 +3646,7 @@
         <v>96</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K10">
         <v>100</v>
@@ -3838,7 +3664,7 @@
         <v>96</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -3861,7 +3687,7 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>100</v>
@@ -3879,7 +3705,7 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -3897,7 +3723,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -3920,7 +3746,7 @@
         <v>100</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>100</v>
@@ -3938,7 +3764,7 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K12">
         <v>100</v>
@@ -3956,7 +3782,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -3979,7 +3805,7 @@
         <v>96</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>100</v>
@@ -3991,13 +3817,13 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I13">
         <v>96</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -4009,13 +3835,13 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O13">
         <v>96</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -4038,7 +3864,7 @@
         <v>100</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>100</v>
@@ -4056,7 +3882,7 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14">
         <v>100</v>
@@ -4074,7 +3900,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -4097,7 +3923,7 @@
         <v>100</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>100</v>
@@ -4115,7 +3941,7 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -4133,7 +3959,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4156,7 +3982,7 @@
         <v>100</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>100</v>
@@ -4174,7 +4000,7 @@
         <v>100</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K16">
         <v>100</v>
@@ -4183,7 +4009,7 @@
         <v>100</v>
       </c>
       <c r="M16">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N16">
         <v>100</v>
@@ -4192,7 +4018,7 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -4201,7 +4027,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4215,7 +4041,7 @@
         <v>92</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17">
         <v>100</v>
@@ -4227,13 +4053,13 @@
         <v>100</v>
       </c>
       <c r="H17">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="I17">
         <v>92</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K17">
         <v>100</v>
@@ -4245,13 +4071,13 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="O17">
         <v>92</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -4274,7 +4100,7 @@
         <v>100</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18">
         <v>100</v>
@@ -4292,7 +4118,7 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K18">
         <v>100</v>
@@ -4310,7 +4136,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -4333,7 +4159,7 @@
         <v>96</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>100</v>
@@ -4351,7 +4177,7 @@
         <v>96</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K19">
         <v>100</v>
@@ -4369,7 +4195,7 @@
         <v>96</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -4392,7 +4218,7 @@
         <v>100</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20">
         <v>100</v>
@@ -4410,7 +4236,7 @@
         <v>100</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20">
         <v>100</v>
@@ -4428,7 +4254,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -4451,7 +4277,7 @@
         <v>100</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21">
         <v>100</v>
@@ -4469,7 +4295,7 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K21">
         <v>100</v>
@@ -4487,7 +4313,7 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -4510,7 +4336,7 @@
         <v>100</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22">
         <v>100</v>
@@ -4528,7 +4354,7 @@
         <v>100</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22">
         <v>100</v>
@@ -4546,7 +4372,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -4569,7 +4395,7 @@
         <v>100</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E23">
         <v>100</v>
@@ -4581,13 +4407,13 @@
         <v>100</v>
       </c>
       <c r="H23">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I23">
         <v>100</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K23">
         <v>100</v>
@@ -4599,13 +4425,13 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O23">
         <v>100</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -4628,7 +4454,7 @@
         <v>96</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>100</v>
@@ -4646,7 +4472,7 @@
         <v>96</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K24">
         <v>100</v>
@@ -4664,7 +4490,7 @@
         <v>96</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -4687,7 +4513,7 @@
         <v>100</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E25">
         <v>100</v>
@@ -4705,7 +4531,7 @@
         <v>100</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K25">
         <v>100</v>
@@ -4723,7 +4549,7 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -4746,7 +4572,7 @@
         <v>96</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E26">
         <v>100</v>
@@ -4764,7 +4590,7 @@
         <v>96</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K26">
         <v>100</v>
@@ -4782,7 +4608,7 @@
         <v>96</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -4805,7 +4631,7 @@
         <v>96</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E27">
         <v>100</v>
@@ -4823,7 +4649,7 @@
         <v>96</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K27">
         <v>100</v>
@@ -4841,7 +4667,7 @@
         <v>96</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -4864,7 +4690,7 @@
         <v>100</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>100</v>
@@ -4882,7 +4708,7 @@
         <v>100</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K28">
         <v>100</v>
@@ -4900,7 +4726,7 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -4923,7 +4749,7 @@
         <v>96</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29">
         <v>100</v>
@@ -4941,7 +4767,7 @@
         <v>96</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K29">
         <v>100</v>
@@ -4959,7 +4785,7 @@
         <v>96</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -4982,7 +4808,7 @@
         <v>100</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E30">
         <v>100</v>
@@ -5000,7 +4826,7 @@
         <v>100</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K30">
         <v>100</v>
@@ -5018,7 +4844,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5041,7 +4867,7 @@
         <v>100</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E31">
         <v>100</v>
@@ -5059,7 +4885,7 @@
         <v>100</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K31">
         <v>100</v>
@@ -5077,7 +4903,7 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -5100,7 +4926,7 @@
         <v>100</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32">
         <v>100</v>
@@ -5118,7 +4944,7 @@
         <v>100</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32">
         <v>100</v>
@@ -5136,7 +4962,7 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -5159,7 +4985,7 @@
         <v>96</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E33">
         <v>100</v>
@@ -5171,13 +4997,13 @@
         <v>100</v>
       </c>
       <c r="H33">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I33">
         <v>96</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K33">
         <v>100</v>
@@ -5189,13 +5015,13 @@
         <v>100</v>
       </c>
       <c r="N33">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O33">
         <v>96</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q33">
         <v>100</v>
@@ -5218,7 +5044,7 @@
         <v>100</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E34">
         <v>100</v>
@@ -5236,7 +5062,7 @@
         <v>100</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K34">
         <v>100</v>
@@ -5254,7 +5080,7 @@
         <v>100</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q34">
         <v>100</v>
@@ -5329,22 +5155,25 @@
         <v>31</v>
       </c>
       <c r="D2">
+        <v>26</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="G2" s="2">
+        <v>16.1</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>31</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5402,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5434,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5466,7 +5295,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5498,7 +5327,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5514,7 +5343,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5541,626 +5370,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920215</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920216</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920033</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" t="s">
-        <v>117</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920217</v>
-      </c>
-      <c r="B5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920219</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D6" t="s">
-        <v>119</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920220</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920221</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>99</v>
-      </c>
-      <c r="D8" t="s">
-        <v>121</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920230</v>
-      </c>
-      <c r="B9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" t="s">
-        <v>96</v>
-      </c>
-      <c r="D9" t="s">
-        <v>122</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920231</v>
-      </c>
-      <c r="B10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D10" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920232</v>
-      </c>
-      <c r="B11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" t="s">
-        <v>124</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920233</v>
-      </c>
-      <c r="B12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" t="s">
-        <v>102</v>
-      </c>
-      <c r="D12" t="s">
-        <v>125</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920042</v>
-      </c>
-      <c r="B13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" t="s">
-        <v>103</v>
-      </c>
-      <c r="D13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920044</v>
-      </c>
-      <c r="B14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920235</v>
-      </c>
-      <c r="B15" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" t="s">
-        <v>128</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920236</v>
-      </c>
-      <c r="B16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" t="s">
-        <v>105</v>
-      </c>
-      <c r="D16" t="s">
-        <v>129</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920239</v>
-      </c>
-      <c r="B17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" t="s">
-        <v>106</v>
-      </c>
-      <c r="D17" t="s">
-        <v>130</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920049</v>
-      </c>
-      <c r="B18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" t="s">
-        <v>96</v>
-      </c>
-      <c r="D18" t="s">
-        <v>131</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920244</v>
-      </c>
-      <c r="B19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" t="s">
-        <v>132</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920246</v>
-      </c>
-      <c r="B20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" t="s">
-        <v>104</v>
-      </c>
-      <c r="D20" t="s">
-        <v>133</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920247</v>
-      </c>
-      <c r="B21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" t="s">
-        <v>134</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920248</v>
-      </c>
-      <c r="B22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D22" t="s">
-        <v>135</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920249</v>
-      </c>
-      <c r="B23" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" t="s">
-        <v>109</v>
-      </c>
-      <c r="D23" t="s">
-        <v>136</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920250</v>
-      </c>
-      <c r="B24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" t="s">
-        <v>110</v>
-      </c>
-      <c r="D24" t="s">
-        <v>137</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920229</v>
-      </c>
-      <c r="B25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" t="s">
-        <v>138</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920228</v>
-      </c>
-      <c r="B26" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" t="s">
-        <v>111</v>
-      </c>
-      <c r="D26" t="s">
-        <v>139</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920066</v>
-      </c>
-      <c r="B27" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" t="s">
-        <v>106</v>
-      </c>
-      <c r="D27" t="s">
-        <v>140</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920227</v>
-      </c>
-      <c r="B28" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" t="s">
-        <v>112</v>
-      </c>
-      <c r="D28" t="s">
-        <v>141</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920226</v>
-      </c>
-      <c r="B29" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" t="s">
-        <v>113</v>
-      </c>
-      <c r="D29" t="s">
-        <v>142</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920224</v>
-      </c>
-      <c r="B30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" t="s">
-        <v>97</v>
-      </c>
-      <c r="D30" t="s">
-        <v>143</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920223</v>
-      </c>
-      <c r="B31" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" t="s">
-        <v>114</v>
-      </c>
-      <c r="D31" t="s">
-        <v>144</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920222</v>
-      </c>
-      <c r="B32" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" t="s">
-        <v>102</v>
-      </c>
-      <c r="D32" t="s">
-        <v>145</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>55</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6168,7 +5377,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6200,22 +5409,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920250</v>
+        <v>21330051920230</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6223,16 +5432,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920250</v>
+        <v>21330051920232</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -6241,27 +5450,27 @@
         <v>55</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920223</v>
+        <v>21330051920235</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6269,16 +5478,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920223</v>
+        <v>21330051920239</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -6287,27 +5496,27 @@
         <v>55</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920222</v>
+        <v>21330051920249</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6315,669 +5524,71 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920222</v>
+        <v>21330051920250</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920215</v>
+        <v>21330051920223</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920216</v>
+        <v>21330051920222</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920033</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920217</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920219</v>
-      </c>
-      <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" t="s">
-        <v>119</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920220</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>98</v>
-      </c>
-      <c r="D13" t="s">
-        <v>120</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920221</v>
-      </c>
-      <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D14" t="s">
-        <v>121</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920230</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D15" t="s">
-        <v>122</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920231</v>
-      </c>
-      <c r="B16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" t="s">
-        <v>123</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920232</v>
-      </c>
-      <c r="B17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" t="s">
-        <v>101</v>
-      </c>
-      <c r="D17" t="s">
-        <v>124</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920233</v>
-      </c>
-      <c r="B18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D18" t="s">
-        <v>125</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920042</v>
-      </c>
-      <c r="B19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" t="s">
-        <v>126</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>55</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920044</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" t="s">
-        <v>104</v>
-      </c>
-      <c r="D20" t="s">
-        <v>127</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920235</v>
-      </c>
-      <c r="B21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" t="s">
-        <v>72</v>
-      </c>
-      <c r="D21" t="s">
-        <v>128</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>55</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920236</v>
-      </c>
-      <c r="B22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" t="s">
-        <v>129</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>55</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920239</v>
-      </c>
-      <c r="B23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" t="s">
-        <v>106</v>
-      </c>
-      <c r="D23" t="s">
-        <v>130</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>55</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920049</v>
-      </c>
-      <c r="B24" t="s">
-        <v>80</v>
-      </c>
-      <c r="C24" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" t="s">
-        <v>131</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>55</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920244</v>
-      </c>
-      <c r="B25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" t="s">
-        <v>101</v>
-      </c>
-      <c r="D25" t="s">
-        <v>132</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>55</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920246</v>
-      </c>
-      <c r="B26" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" t="s">
-        <v>104</v>
-      </c>
-      <c r="D26" t="s">
-        <v>133</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>55</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920247</v>
-      </c>
-      <c r="B27" t="s">
-        <v>83</v>
-      </c>
-      <c r="C27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D27" t="s">
-        <v>134</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>55</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920248</v>
-      </c>
-      <c r="B28" t="s">
-        <v>84</v>
-      </c>
-      <c r="C28" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" t="s">
-        <v>135</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>55</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920249</v>
-      </c>
-      <c r="B29" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" t="s">
-        <v>109</v>
-      </c>
-      <c r="D29" t="s">
-        <v>136</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>55</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920229</v>
-      </c>
-      <c r="B30" t="s">
-        <v>86</v>
-      </c>
-      <c r="C30" t="s">
-        <v>81</v>
-      </c>
-      <c r="D30" t="s">
-        <v>138</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>55</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>21330051920228</v>
-      </c>
-      <c r="B31" t="s">
-        <v>87</v>
-      </c>
-      <c r="C31" t="s">
-        <v>111</v>
-      </c>
-      <c r="D31" t="s">
-        <v>139</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>55</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>21330051920066</v>
-      </c>
-      <c r="B32" t="s">
-        <v>88</v>
-      </c>
-      <c r="C32" t="s">
-        <v>106</v>
-      </c>
-      <c r="D32" t="s">
-        <v>140</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>55</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>21330051920227</v>
-      </c>
-      <c r="B33" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" t="s">
-        <v>141</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>55</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>21330051920226</v>
-      </c>
-      <c r="B34" t="s">
-        <v>90</v>
-      </c>
-      <c r="C34" t="s">
-        <v>113</v>
-      </c>
-      <c r="D34" t="s">
-        <v>142</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>55</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>21330051920224</v>
-      </c>
-      <c r="B35" t="s">
-        <v>91</v>
-      </c>
-      <c r="C35" t="s">
-        <v>97</v>
-      </c>
-      <c r="D35" t="s">
-        <v>143</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>55</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5ARHM - Estadisticos 20231.xlsx
+++ b/grupos/5ARHM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="79">
   <si>
     <t>Materia</t>
   </si>
@@ -218,67 +218,40 @@
     <t>CRUZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>MADRIGAL</t>
-  </si>
-  <si>
     <t>TEHUINTLE</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>ZACAMECAHUA</t>
-  </si>
-  <si>
     <t>ZEPEDA</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>MARES</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>TZANAHUA</t>
   </si>
   <si>
     <t>PORTILLA</t>
   </si>
   <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
-    <t>ALONDRA VANNESSA</t>
-  </si>
-  <si>
     <t>LIZBETH JOSELYN</t>
   </si>
   <si>
-    <t>AMERICA PAOLA</t>
-  </si>
-  <si>
     <t>LUCERO</t>
   </si>
   <si>
     <t>GETSEMANI GUADALUPE</t>
-  </si>
-  <si>
-    <t>HARUMI</t>
   </si>
   <si>
     <t>YAEL</t>
@@ -792,10 +765,10 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>10</v>
@@ -869,10 +842,10 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -905,10 +878,10 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -946,10 +919,10 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>9</v>
@@ -985,7 +958,7 @@
         <v>9</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1023,10 +996,10 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
         <v>9</v>
@@ -1059,10 +1032,10 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -1100,10 +1073,10 @@
         <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>9</v>
@@ -1139,7 +1112,7 @@
         <v>8</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1177,10 +1150,10 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
         <v>9</v>
@@ -1254,10 +1227,10 @@
         <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
         <v>9</v>
@@ -1290,10 +1263,10 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1331,10 +1304,10 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
         <v>10</v>
@@ -1408,10 +1381,10 @@
         <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
         <v>9</v>
@@ -1444,10 +1417,10 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1485,10 +1458,10 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>10</v>
@@ -1562,10 +1535,10 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
         <v>9</v>
@@ -1598,10 +1571,10 @@
         <v>10</v>
       </c>
       <c r="U14">
+        <v>8</v>
+      </c>
+      <c r="V14">
         <v>7</v>
-      </c>
-      <c r="V14">
-        <v>5</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -1639,10 +1612,10 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
         <v>10</v>
@@ -1678,7 +1651,7 @@
         <v>9</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>10</v>
@@ -1716,10 +1689,10 @@
         <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
         <v>9</v>
@@ -1752,10 +1725,10 @@
         <v>9</v>
       </c>
       <c r="U16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -1793,10 +1766,10 @@
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
         <v>9</v>
@@ -1870,10 +1843,10 @@
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
         <v>10</v>
@@ -1909,7 +1882,7 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>10</v>
@@ -1947,10 +1920,10 @@
         <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
         <v>10</v>
@@ -1983,10 +1956,10 @@
         <v>10</v>
       </c>
       <c r="U19">
+        <v>7</v>
+      </c>
+      <c r="V19">
         <v>6</v>
-      </c>
-      <c r="V19">
-        <v>5</v>
       </c>
       <c r="W19">
         <v>10</v>
@@ -2024,10 +1997,10 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
         <v>10</v>
@@ -2101,10 +2074,10 @@
         <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
         <v>9</v>
@@ -2137,10 +2110,10 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2178,10 +2151,10 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
         <v>9</v>
@@ -2214,10 +2187,10 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>9</v>
@@ -2255,10 +2228,10 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
         <v>9</v>
@@ -2291,10 +2264,10 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -2332,10 +2305,10 @@
         <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
         <v>9</v>
@@ -2409,10 +2382,10 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
         <v>10</v>
@@ -2445,10 +2418,10 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2486,10 +2459,10 @@
         <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
         <v>10</v>
@@ -2563,10 +2536,10 @@
         <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
         <v>10</v>
@@ -2640,10 +2613,10 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
         <v>9</v>
@@ -2679,7 +2652,7 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -2717,10 +2690,10 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
         <v>9</v>
@@ -2756,7 +2729,7 @@
         <v>7</v>
       </c>
       <c r="V29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -2794,10 +2767,10 @@
         <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
         <v>9</v>
@@ -2830,10 +2803,10 @@
         <v>10</v>
       </c>
       <c r="U30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -2871,10 +2844,10 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
         <v>10</v>
@@ -2910,7 +2883,7 @@
         <v>10</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W31">
         <v>10</v>
@@ -2948,10 +2921,10 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
         <v>9</v>
@@ -2984,10 +2957,10 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W32">
         <v>9</v>
@@ -3025,10 +2998,10 @@
         <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
         <v>9</v>
@@ -3061,7 +3034,7 @@
         <v>9</v>
       </c>
       <c r="U33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V33">
         <v>6</v>
@@ -3102,10 +3075,10 @@
         <v>7</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
         <v>9</v>
@@ -3141,7 +3114,7 @@
         <v>5</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W34">
         <v>9</v>
@@ -3348,7 +3321,7 @@
         <v>97.5</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J5">
         <v>100</v>
@@ -3366,7 +3339,7 @@
         <v>97.5</v>
       </c>
       <c r="O5">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -3466,7 +3439,7 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -3484,7 +3457,7 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -3525,7 +3498,7 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -3543,7 +3516,7 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -3643,10 +3616,10 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J10">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="K10">
         <v>100</v>
@@ -3661,10 +3634,10 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="P10">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -3882,7 +3855,7 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K14">
         <v>100</v>
@@ -3900,7 +3873,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -3938,7 +3911,7 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -3956,7 +3929,7 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -3997,7 +3970,7 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J16">
         <v>100</v>
@@ -4015,7 +3988,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -4056,7 +4029,7 @@
         <v>87.5</v>
       </c>
       <c r="I17">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="J17">
         <v>100</v>
@@ -4074,7 +4047,7 @@
         <v>87.5</v>
       </c>
       <c r="O17">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -4174,7 +4147,7 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J19">
         <v>100</v>
@@ -4192,7 +4165,7 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -4351,7 +4324,7 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J22">
         <v>100</v>
@@ -4369,7 +4342,7 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -4410,7 +4383,7 @@
         <v>95</v>
       </c>
       <c r="I23">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J23">
         <v>100</v>
@@ -4428,7 +4401,7 @@
         <v>95</v>
       </c>
       <c r="O23">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P23">
         <v>100</v>
@@ -4587,7 +4560,7 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J26">
         <v>100</v>
@@ -4605,7 +4578,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -4646,7 +4619,7 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J27">
         <v>100</v>
@@ -4664,7 +4637,7 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P27">
         <v>100</v>
@@ -4823,7 +4796,7 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J30">
         <v>100</v>
@@ -4841,7 +4814,7 @@
         <v>100</v>
       </c>
       <c r="O30">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -4882,7 +4855,7 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J31">
         <v>100</v>
@@ -4900,7 +4873,7 @@
         <v>100</v>
       </c>
       <c r="O31">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P31">
         <v>100</v>
@@ -4941,7 +4914,7 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J32">
         <v>100</v>
@@ -4959,7 +4932,7 @@
         <v>100</v>
       </c>
       <c r="O32">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P32">
         <v>100</v>
@@ -5059,7 +5032,7 @@
         <v>100</v>
       </c>
       <c r="I34">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J34">
         <v>100</v>
@@ -5077,7 +5050,7 @@
         <v>100</v>
       </c>
       <c r="O34">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P34">
         <v>100</v>
@@ -5155,19 +5128,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2">
-        <v>83.90000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="G2" s="2">
-        <v>16.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5187,19 +5160,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>90.3</v>
+        <v>93.5</v>
       </c>
       <c r="G3" s="2">
-        <v>9.699999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5377,7 +5350,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5415,10 +5388,10 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -5432,16 +5405,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920232</v>
+        <v>21330051920235</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -5455,16 +5428,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920235</v>
+        <v>21330051920249</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -5478,22 +5451,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920239</v>
+        <v>21330051920250</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5501,93 +5474,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920249</v>
+        <v>21330051920222</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920250</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920223</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920222</v>
-      </c>
-      <c r="B9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ARHM - Estadisticos 20231.xlsx
+++ b/grupos/5ARHM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="68">
   <si>
     <t>Materia</t>
   </si>
@@ -188,15 +188,15 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Medina Tolentino Elio</t>
   </si>
   <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
     <t>Castro Vasquez Julieta</t>
   </si>
   <si>
@@ -215,46 +215,13 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>GETSEMANI GUADALUPE</t>
-  </si>
-  <si>
-    <t>YAEL</t>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>KARINA</t>
   </si>
 </sst>
 </file>
@@ -780,22 +747,22 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -857,31 +824,31 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>8</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -934,22 +901,22 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -958,7 +925,7 @@
         <v>9</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1011,22 +978,22 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1088,25 +1055,25 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>8</v>
@@ -1165,25 +1132,25 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>6</v>
@@ -1198,7 +1165,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1242,22 +1209,22 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1266,7 +1233,7 @@
         <v>8</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1319,31 +1286,31 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>8</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -1396,22 +1363,22 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1420,7 +1387,7 @@
         <v>9</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1473,31 +1440,31 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>7</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1550,25 +1517,25 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -1627,31 +1594,31 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>9</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>10</v>
@@ -1704,22 +1671,22 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -1737,7 +1704,7 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1781,37 +1748,37 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>6</v>
       </c>
       <c r="V17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>9</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -1858,22 +1825,22 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -1935,22 +1902,22 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -1959,7 +1926,7 @@
         <v>7</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>10</v>
@@ -2012,22 +1979,22 @@
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2089,22 +2056,22 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2166,22 +2133,22 @@
         <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2243,22 +2210,22 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>10</v>
@@ -2320,22 +2287,22 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>9</v>
@@ -2344,13 +2311,13 @@
         <v>6</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>9</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>9</v>
@@ -2397,22 +2364,22 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2474,22 +2441,22 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2551,28 +2518,28 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
       </c>
       <c r="U27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V27">
         <v>6</v>
@@ -2628,22 +2595,22 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2705,22 +2672,22 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -2782,22 +2749,22 @@
         <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -2859,22 +2826,22 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -2936,22 +2903,22 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -3013,22 +2980,22 @@
         <v>8</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>9</v>
@@ -3037,7 +3004,7 @@
         <v>7</v>
       </c>
       <c r="V33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W33">
         <v>9</v>
@@ -3046,7 +3013,7 @@
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3090,28 +3057,28 @@
         <v>8</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V34">
         <v>7</v>
@@ -3277,7 +3244,7 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -3286,7 +3253,7 @@
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>98</v>
+        <v>97.3</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -3336,10 +3303,10 @@
         <v>100</v>
       </c>
       <c r="N5">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="O5">
         <v>97.5</v>
-      </c>
-      <c r="O5">
-        <v>96</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -3457,7 +3424,7 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -3516,7 +3483,7 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -3572,10 +3539,10 @@
         <v>100</v>
       </c>
       <c r="N9">
+        <v>95.3</v>
+      </c>
+      <c r="O9">
         <v>95</v>
-      </c>
-      <c r="O9">
-        <v>92</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -3634,10 +3601,10 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="P10">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -3808,10 +3775,10 @@
         <v>100</v>
       </c>
       <c r="N13">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="O13">
         <v>97.5</v>
-      </c>
-      <c r="O13">
-        <v>96</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -3873,7 +3840,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -3929,7 +3896,7 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -3988,7 +3955,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -4000,7 +3967,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4044,10 +4011,10 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>87.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O17">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -4165,7 +4132,7 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -4339,10 +4306,10 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O22">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -4398,10 +4365,10 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O23">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="P23">
         <v>100</v>
@@ -4460,7 +4427,7 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -4578,7 +4545,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -4637,7 +4604,7 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="P27">
         <v>100</v>
@@ -4755,7 +4722,7 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="P29">
         <v>100</v>
@@ -4814,7 +4781,7 @@
         <v>100</v>
       </c>
       <c r="O30">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -4873,7 +4840,7 @@
         <v>100</v>
       </c>
       <c r="O31">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="P31">
         <v>100</v>
@@ -4932,7 +4899,7 @@
         <v>100</v>
       </c>
       <c r="O32">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="P32">
         <v>100</v>
@@ -4988,10 +4955,10 @@
         <v>100</v>
       </c>
       <c r="N33">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O33">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -5050,7 +5017,7 @@
         <v>100</v>
       </c>
       <c r="O34">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="P34">
         <v>100</v>
@@ -5128,16 +5095,16 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
-        <v>90.3</v>
+        <v>96.8</v>
       </c>
       <c r="G2" s="2">
-        <v>9.699999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="H2">
         <v>7.7</v>
@@ -5151,7 +5118,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -5160,19 +5127,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>93.5</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>9.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5183,7 +5150,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -5204,7 +5171,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5215,7 +5182,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -5236,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5268,7 +5235,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5300,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5350,7 +5317,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5382,16 +5349,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920230</v>
+        <v>21330051920221</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -5400,98 +5367,6 @@
         <v>55</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920235</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920249</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920250</v>
-      </c>
-      <c r="B5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920222</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ARHM - Estadisticos 20231.xlsx
+++ b/grupos/5ARHM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="65">
   <si>
     <t>Materia</t>
   </si>
@@ -185,18 +185,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
     <t>Castro Vasquez Julieta</t>
   </si>
   <si>
@@ -213,15 +213,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>KARINA</t>
   </si>
 </sst>
 </file>
@@ -1233,7 +1224,7 @@
         <v>8</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -3568,7 +3559,7 @@
         <v>96</v>
       </c>
       <c r="D10">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>100</v>
@@ -3586,7 +3577,7 @@
         <v>94</v>
       </c>
       <c r="J10">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>100</v>
@@ -3604,7 +3595,7 @@
         <v>96.3</v>
       </c>
       <c r="P10">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -5086,7 +5077,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -5095,19 +5086,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>9.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5118,7 +5109,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -5139,7 +5130,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5150,7 +5141,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -5171,7 +5162,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9.5</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5182,7 +5173,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -5203,7 +5194,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5317,7 +5308,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5347,29 +5338,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920221</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/5ARHM - Estadisticos 20231.xlsx
+++ b/grupos/5ARHM - Estadisticos 20231.xlsx
@@ -762,7 +762,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -833,13 +833,13 @@
         <v>10</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -913,13 +913,13 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -990,16 +990,16 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1064,22 +1064,22 @@
         <v>10</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1141,22 +1141,22 @@
         <v>10</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1221,13 +1221,13 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1295,19 +1295,19 @@
         <v>10</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>10</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1375,13 +1375,13 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1449,13 +1449,13 @@
         <v>10</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1526,22 +1526,22 @@
         <v>8</v>
       </c>
       <c r="T14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1603,13 +1603,13 @@
         <v>10</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>10</v>
@@ -1680,22 +1680,22 @@
         <v>10</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1757,22 +1757,22 @@
         <v>7</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1837,10 +1837,10 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>10</v>
@@ -1914,16 +1914,16 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>10</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y19">
         <v>10</v>
@@ -1994,7 +1994,7 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>10</v>
@@ -2068,19 +2068,19 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2145,19 +2145,19 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2222,16 +2222,16 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y23">
         <v>10</v>
@@ -2296,22 +2296,22 @@
         <v>10</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2376,10 +2376,10 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2530,10 +2530,10 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -2610,10 +2610,10 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -2684,13 +2684,13 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -2761,13 +2761,13 @@
         <v>10</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X30">
         <v>10</v>
@@ -2915,13 +2915,13 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -2989,22 +2989,22 @@
         <v>10</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3066,22 +3066,22 @@
         <v>10</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -5098,7 +5098,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5130,7 +5130,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5162,7 +5162,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5194,7 +5194,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5226,7 +5226,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/5ARHM - Estadisticos 20231.xlsx
+++ b/grupos/5ARHM - Estadisticos 20231.xlsx
@@ -762,7 +762,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -833,13 +833,13 @@
         <v>10</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -913,13 +913,13 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -990,16 +990,16 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1064,22 +1064,22 @@
         <v>10</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1141,22 +1141,22 @@
         <v>10</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1221,13 +1221,13 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1295,19 +1295,19 @@
         <v>10</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>10</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1375,13 +1375,13 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1449,13 +1449,13 @@
         <v>10</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1526,22 +1526,22 @@
         <v>8</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1603,13 +1603,13 @@
         <v>10</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>10</v>
@@ -1680,22 +1680,22 @@
         <v>10</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1757,22 +1757,22 @@
         <v>7</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1837,10 +1837,10 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>10</v>
@@ -1914,16 +1914,16 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>10</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>10</v>
@@ -1994,7 +1994,7 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>10</v>
@@ -2068,19 +2068,19 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2145,19 +2145,19 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2222,16 +2222,16 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>10</v>
@@ -2296,22 +2296,22 @@
         <v>10</v>
       </c>
       <c r="T24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2376,10 +2376,10 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2530,10 +2530,10 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -2610,10 +2610,10 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -2684,13 +2684,13 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -2761,13 +2761,13 @@
         <v>10</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>10</v>
@@ -2915,13 +2915,13 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -2989,22 +2989,22 @@
         <v>10</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3066,22 +3066,22 @@
         <v>10</v>
       </c>
       <c r="T34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y34">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -5098,7 +5098,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5130,7 +5130,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5162,7 +5162,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5194,7 +5194,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5226,7 +5226,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
